--- a/invoice_system_management/static/excel/allInvoices.xlsx
+++ b/invoice_system_management/static/excel/allInvoices.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -438,9 +438,8 @@
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,15 +475,10 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>product_price</t>
+          <t>product_unit</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>product_amount</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>invoice_total</t>
         </is>
@@ -492,34 +486,436 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>45436</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ishaan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>82727293729</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>45436</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>kanishk</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>71371922</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ishaan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>82727293729</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ishaan</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>82727293729</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B6" s="3" t="n">
         <v>45439</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ravi</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>111111111111</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Cycle</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>100</v>
       </c>
-      <c r="H2" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" t="n">
-        <v>472</v>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1002.21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>46.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>wewew</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>e3e34343</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>1000.5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>45439</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wewew</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>e3e34343</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>bike</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>2000.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>wewew</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>e3e34343</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>bat</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ravi</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>111111111111</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>bat</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>45455</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ishaan</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>82727293729</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Cycle</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
